--- a/PicoTracker_1.xlsx
+++ b/PicoTracker_1.xlsx
@@ -8,20 +8,34 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/davidthrower/Documents/My Documents/Claude Context/Pico Balloons/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9039CF03-7509-654B-A933-82872CA063A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{456ECF30-1341-D04F-9C6C-0EF20B5864EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="34560" windowHeight="20160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4360" yWindow="680" windowWidth="30200" windowHeight="20160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Flight Paths" sheetId="2" r:id="rId2"/>
+    <sheet name="Tracker" sheetId="1" r:id="rId1"/>
+    <sheet name="Weight" sheetId="3" r:id="rId2"/>
+    <sheet name="Flight Paths" sheetId="2" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="56">
   <si>
     <t>PICO Balloon Tracker</t>
   </si>
@@ -47,9 +61,6 @@
     <t>General</t>
   </si>
   <si>
-    <t>Number</t>
-  </si>
-  <si>
     <t>Date</t>
   </si>
   <si>
@@ -110,9 +121,6 @@
     <t>H2</t>
   </si>
   <si>
-    <t>4325mm</t>
-  </si>
-  <si>
     <t>Solar System</t>
   </si>
   <si>
@@ -174,6 +182,27 @@
   </si>
   <si>
     <t>Note:  KML flie is the google earth path.  Export from live maps for an archive</t>
+  </si>
+  <si>
+    <t>4625mm</t>
+  </si>
+  <si>
+    <t>Weight</t>
+  </si>
+  <si>
+    <t>Antennas</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Tracker</t>
+  </si>
+  <si>
+    <t>Connections</t>
+  </si>
+  <si>
+    <t>Payload</t>
   </si>
 </sst>
 </file>
@@ -631,7 +660,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S13"/>
+  <dimension ref="A1:T13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="21.33203125" customWidth="1"/>
@@ -641,114 +670,117 @@
     <col min="5" max="5" width="13.1640625" style="5" customWidth="1"/>
     <col min="6" max="7" width="16.83203125" style="5" customWidth="1"/>
     <col min="8" max="9" width="20.6640625" style="5" customWidth="1"/>
-    <col min="10" max="10" width="14" style="5" customWidth="1"/>
-    <col min="11" max="11" width="16.5" style="5" customWidth="1"/>
-    <col min="12" max="12" width="35.33203125" customWidth="1"/>
-    <col min="13" max="14" width="10.83203125" style="4" customWidth="1"/>
-    <col min="15" max="15" width="13" style="4" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="13" style="4" customWidth="1"/>
-    <col min="18" max="18" width="84" style="4" customWidth="1"/>
-    <col min="19" max="19" width="16" customWidth="1"/>
+    <col min="10" max="11" width="14" style="5" customWidth="1"/>
+    <col min="12" max="12" width="16.5" style="5" customWidth="1"/>
+    <col min="13" max="13" width="35.33203125" customWidth="1"/>
+    <col min="14" max="15" width="10.83203125" style="4" customWidth="1"/>
+    <col min="16" max="16" width="13" style="4" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="13" style="4" customWidth="1"/>
+    <col min="19" max="19" width="84" style="4" customWidth="1"/>
+    <col min="20" max="20" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="19" customHeight="1">
+    <row r="1" spans="1:20" ht="19" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="19" customHeight="1">
+    <row r="2" spans="1:20" ht="19" customHeight="1">
       <c r="A2" s="2">
         <v>46203</v>
       </c>
     </row>
-    <row r="3" spans="1:19">
+    <row r="3" spans="1:20">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:19" s="7" customFormat="1">
+    <row r="6" spans="1:20" s="7" customFormat="1">
       <c r="B6" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="L6" s="8" t="s">
-        <v>3</v>
-      </c>
       <c r="M6" s="8" t="s">
         <v>3</v>
       </c>
       <c r="N6" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="O6" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="O6" s="8" t="s">
+      <c r="P6" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="P6" s="8" t="s">
+      <c r="Q6" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="Q6" s="8" t="s">
+      <c r="R6" s="8" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:19" s="7" customFormat="1">
+    <row r="7" spans="1:20" s="7" customFormat="1">
       <c r="A7" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="C7" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="D7" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="E7" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="F7" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="G7" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="H7" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="H7" s="7" t="s">
+      <c r="I7" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="I7" s="7" t="s">
+      <c r="J7" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="J7" s="7" t="s">
+      <c r="K7" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="L7" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="K7" s="7" t="s">
+      <c r="M7" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="N7" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="L7" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="M7" s="8" t="s">
+      <c r="O7" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="N7" s="8" t="s">
+      <c r="P7" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="O7" s="8" t="s">
+      <c r="Q7" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="P7" s="8" t="s">
+      <c r="R7" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="Q7" s="8" t="s">
+      <c r="S7" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="R7" s="7" t="s">
+      <c r="T7" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="S7" s="9" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19">
+    </row>
+    <row r="8" spans="1:20">
       <c r="A8" s="5">
         <v>1</v>
       </c>
@@ -757,150 +789,274 @@
         <v>290</v>
       </c>
       <c r="D8" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="H8" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="H8" s="5" t="s">
+      <c r="I8" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="J8" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="I8" s="5" t="s">
+      <c r="M8" s="4"/>
+      <c r="T8" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="J8" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="L8" s="4"/>
-      <c r="S8" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19">
+    </row>
+    <row r="9" spans="1:20">
       <c r="A9" s="5">
         <v>2</v>
       </c>
       <c r="B9" s="6"/>
-      <c r="C9" s="5">
-        <v>291</v>
-      </c>
+      <c r="C9" s="5"/>
       <c r="D9" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="H9" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="H9" s="5" t="s">
-        <v>28</v>
-      </c>
       <c r="I9" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="M9" s="4"/>
+      <c r="T9" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="J9" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="L9" s="4"/>
-      <c r="S9" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19">
+    </row>
+    <row r="10" spans="1:20">
       <c r="A10" s="5">
         <v>3</v>
       </c>
       <c r="B10" s="6"/>
-      <c r="C10" s="5">
-        <v>292</v>
-      </c>
+      <c r="C10" s="5"/>
       <c r="D10" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="H10" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="H10" s="5" t="s">
-        <v>28</v>
-      </c>
       <c r="I10" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="M10" s="4"/>
+      <c r="T10" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="J10" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="L10" s="4"/>
-      <c r="S10" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19">
+    </row>
+    <row r="11" spans="1:20">
       <c r="A11" s="5">
         <v>4</v>
       </c>
       <c r="B11" s="6"/>
-      <c r="C11" s="5"/>
+      <c r="C11" s="5">
+        <v>290</v>
+      </c>
       <c r="D11" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="H11" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="H11" s="5" t="s">
-        <v>28</v>
-      </c>
       <c r="I11" s="5" t="s">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="L11" s="4"/>
-      <c r="S11" s="11" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19">
+        <v>30</v>
+      </c>
+      <c r="M11" s="4"/>
+      <c r="T11" s="11" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20">
       <c r="A12" s="5">
         <v>5</v>
       </c>
       <c r="B12" s="6"/>
-      <c r="C12" s="5"/>
+      <c r="C12" s="5">
+        <v>292</v>
+      </c>
       <c r="D12" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E12" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="H12" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="H12" s="5" t="s">
-        <v>28</v>
-      </c>
       <c r="I12" s="5" t="s">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="L12" s="4"/>
-      <c r="S12" s="11" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19">
+        <v>30</v>
+      </c>
+      <c r="M12" s="4"/>
+      <c r="T12" s="11" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20">
       <c r="A13" s="5"/>
       <c r="B13" s="6"/>
       <c r="C13" s="5"/>
-      <c r="L13" s="4"/>
+      <c r="M13" s="4"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="S8" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="S9" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="S10" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="T8" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="T9" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="T10" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE71AB22-6A7E-FB44-9621-B06B132CDAE6}">
+  <dimension ref="B3:I9"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <cols>
+    <col min="2" max="9" width="10.83203125" style="5"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:8">
+      <c r="F3" s="7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4" spans="2:8" s="7" customFormat="1">
+      <c r="B4" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8">
+      <c r="B5" s="5">
+        <v>1</v>
+      </c>
+      <c r="C5" s="5">
+        <v>6</v>
+      </c>
+      <c r="D5" s="5">
+        <v>16</v>
+      </c>
+      <c r="F5" s="5">
+        <f>SUM(C5:E5)</f>
+        <v>22</v>
+      </c>
+      <c r="H5" s="5">
+        <f>G5+F5</f>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8">
+      <c r="B6" s="5">
+        <v>2</v>
+      </c>
+      <c r="C6" s="5">
+        <v>6</v>
+      </c>
+      <c r="F6" s="5">
+        <f t="shared" ref="F6:F9" si="0">SUM(C6:E6)</f>
+        <v>6</v>
+      </c>
+      <c r="H6" s="5">
+        <f t="shared" ref="H6:H9" si="1">G6+F6</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8">
+      <c r="B7" s="5">
+        <v>3</v>
+      </c>
+      <c r="C7" s="5">
+        <v>6</v>
+      </c>
+      <c r="F7" s="5">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="H7" s="5">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8">
+      <c r="B8" s="5">
+        <v>4</v>
+      </c>
+      <c r="C8" s="5">
+        <v>6</v>
+      </c>
+      <c r="D8" s="5">
+        <v>12</v>
+      </c>
+      <c r="F8" s="5">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="H8" s="5">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8">
+      <c r="B9" s="5">
+        <v>5</v>
+      </c>
+      <c r="C9" s="5">
+        <v>6</v>
+      </c>
+      <c r="D9" s="5">
+        <v>12</v>
+      </c>
+      <c r="F9" s="5">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="H9" s="5">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
@@ -915,112 +1071,112 @@
   <sheetData>
     <row r="1" spans="1:6" ht="19">
       <c r="A1" s="12" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="13" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="B5" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="9" t="s">
+      <c r="F5" s="9" t="s">
         <v>37</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="150" customHeight="1">
       <c r="A6" s="14" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B6" s="14">
         <v>290</v>
       </c>
       <c r="C6" s="14"/>
       <c r="D6" s="10" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E6" s="16" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F6" s="15"/>
     </row>
     <row r="7" spans="1:6" ht="150" customHeight="1">
       <c r="A7" s="14" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B7" s="14">
         <v>291</v>
       </c>
       <c r="C7" s="14"/>
       <c r="D7" s="10" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E7" s="16" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F7" s="15"/>
     </row>
     <row r="8" spans="1:6" ht="150" customHeight="1">
       <c r="A8" s="14" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B8" s="14">
         <v>292</v>
       </c>
       <c r="C8" s="14"/>
       <c r="D8" s="10" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E8" s="16" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F8" s="15"/>
     </row>
     <row r="9" spans="1:6" ht="150" customHeight="1">
       <c r="A9" s="14" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B9" s="14"/>
       <c r="C9" s="14"/>
       <c r="D9" s="11" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E9" s="17" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F9" s="15"/>
     </row>
     <row r="10" spans="1:6" ht="150" customHeight="1">
       <c r="A10" s="14" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B10" s="14"/>
       <c r="C10" s="14"/>
       <c r="D10" s="11" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E10" s="17" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F10" s="15"/>
     </row>

--- a/PicoTracker_1.xlsx
+++ b/PicoTracker_1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/davidthrower/Documents/My Documents/Claude Context/Pico Balloons/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{456ECF30-1341-D04F-9C6C-0EF20B5864EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1417D15D-68B2-1842-A7DF-3B62191AE636}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4360" yWindow="680" windowWidth="30200" windowHeight="20160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4360" yWindow="680" windowWidth="30200" windowHeight="20160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tracker" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="58">
   <si>
     <t>PICO Balloon Tracker</t>
   </si>
@@ -203,6 +203,12 @@
   </si>
   <si>
     <t>Payload</t>
+  </si>
+  <si>
+    <t>Checked</t>
+  </si>
+  <si>
+    <t>Ground</t>
   </si>
 </sst>
 </file>
@@ -660,267 +666,284 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T13"/>
+  <dimension ref="A1:U13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="21.33203125" customWidth="1"/>
-    <col min="2" max="2" width="10.83203125" style="5" customWidth="1"/>
-    <col min="3" max="3" width="12" style="6" customWidth="1"/>
-    <col min="4" max="4" width="14.33203125" style="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.1640625" style="5" customWidth="1"/>
-    <col min="6" max="7" width="16.83203125" style="5" customWidth="1"/>
-    <col min="8" max="9" width="20.6640625" style="5" customWidth="1"/>
-    <col min="10" max="11" width="14" style="5" customWidth="1"/>
-    <col min="12" max="12" width="16.5" style="5" customWidth="1"/>
-    <col min="13" max="13" width="35.33203125" customWidth="1"/>
-    <col min="14" max="15" width="10.83203125" style="4" customWidth="1"/>
-    <col min="16" max="16" width="13" style="4" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="13" style="4" customWidth="1"/>
-    <col min="19" max="19" width="84" style="4" customWidth="1"/>
-    <col min="20" max="20" width="16" customWidth="1"/>
+    <col min="1" max="2" width="21.33203125" customWidth="1"/>
+    <col min="3" max="3" width="10.83203125" style="5" customWidth="1"/>
+    <col min="4" max="4" width="12" style="6" customWidth="1"/>
+    <col min="5" max="5" width="14.33203125" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.1640625" style="5" customWidth="1"/>
+    <col min="7" max="8" width="16.83203125" style="5" customWidth="1"/>
+    <col min="9" max="10" width="20.6640625" style="5" customWidth="1"/>
+    <col min="11" max="12" width="14" style="5" customWidth="1"/>
+    <col min="13" max="13" width="16.5" style="5" customWidth="1"/>
+    <col min="14" max="14" width="35.33203125" customWidth="1"/>
+    <col min="15" max="16" width="10.83203125" style="4" customWidth="1"/>
+    <col min="17" max="17" width="13" style="4" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="13" style="4" customWidth="1"/>
+    <col min="20" max="20" width="84" style="4" customWidth="1"/>
+    <col min="21" max="21" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="19" customHeight="1">
+    <row r="1" spans="1:21" ht="19" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:20" ht="19" customHeight="1">
+      <c r="B1" s="1"/>
+    </row>
+    <row r="2" spans="1:21" ht="19" customHeight="1">
       <c r="A2" s="2">
         <v>46203</v>
       </c>
-    </row>
-    <row r="3" spans="1:20">
+      <c r="B2" s="2"/>
+    </row>
+    <row r="3" spans="1:21">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:20" s="7" customFormat="1">
-      <c r="B6" s="8" t="s">
+      <c r="B3" s="3"/>
+    </row>
+    <row r="6" spans="1:21" s="7" customFormat="1">
+      <c r="B6" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C6" s="8" t="s">
         <v>2</v>
-      </c>
-      <c r="M6" s="8" t="s">
-        <v>3</v>
       </c>
       <c r="N6" s="8" t="s">
         <v>3</v>
       </c>
       <c r="O6" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="P6" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="P6" s="8" t="s">
+      <c r="Q6" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="Q6" s="8" t="s">
+      <c r="R6" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="R6" s="8" t="s">
+      <c r="S6" s="8" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:20" s="7" customFormat="1">
+    <row r="7" spans="1:21" s="7" customFormat="1">
       <c r="A7" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C7" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="D7" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="E7" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="F7" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="G7" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="H7" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="H7" s="7" t="s">
+      <c r="I7" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="I7" s="7" t="s">
+      <c r="J7" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="J7" s="7" t="s">
+      <c r="K7" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="K7" s="7" t="s">
+      <c r="L7" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="L7" s="7" t="s">
+      <c r="M7" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="M7" s="8" t="s">
+      <c r="N7" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="N7" s="8" t="s">
+      <c r="O7" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="O7" s="8" t="s">
+      <c r="P7" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="P7" s="8" t="s">
+      <c r="Q7" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="Q7" s="8" t="s">
+      <c r="R7" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="R7" s="8" t="s">
+      <c r="S7" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="S7" s="7" t="s">
+      <c r="T7" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="T7" s="9" t="s">
+      <c r="U7" s="9" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="1:20">
+    <row r="8" spans="1:21">
       <c r="A8" s="5">
         <v>1</v>
       </c>
       <c r="B8" s="6"/>
-      <c r="C8" s="5">
+      <c r="C8" s="6"/>
+      <c r="D8" s="5">
         <v>290</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="E8" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="F8" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="H8" s="5" t="s">
+      <c r="I8" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="I8" s="5" t="s">
+      <c r="J8" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="J8" s="5" t="s">
+      <c r="K8" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="M8" s="4"/>
-      <c r="T8" s="10" t="s">
+      <c r="N8" s="4"/>
+      <c r="U8" s="10" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:20">
+    <row r="9" spans="1:21">
       <c r="A9" s="5">
         <v>2</v>
       </c>
       <c r="B9" s="6"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5" t="s">
+      <c r="C9" s="6"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="F9" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="H9" s="5" t="s">
+      <c r="I9" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="I9" s="5" t="s">
+      <c r="J9" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="M9" s="4"/>
-      <c r="T9" s="10" t="s">
+      <c r="N9" s="4"/>
+      <c r="U9" s="10" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:20">
+    <row r="10" spans="1:21">
       <c r="A10" s="5">
         <v>3</v>
       </c>
       <c r="B10" s="6"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5" t="s">
+      <c r="C10" s="6"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="F10" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="H10" s="5" t="s">
+      <c r="I10" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="I10" s="5" t="s">
+      <c r="J10" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="M10" s="4"/>
-      <c r="T10" s="10" t="s">
+      <c r="N10" s="4"/>
+      <c r="U10" s="10" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="1:20">
+    <row r="11" spans="1:21">
       <c r="A11" s="5">
         <v>4</v>
       </c>
-      <c r="B11" s="6"/>
-      <c r="C11" s="5">
+      <c r="B11" s="6">
+        <v>46203</v>
+      </c>
+      <c r="C11" s="6"/>
+      <c r="D11" s="5">
         <v>290</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="E11" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="F11" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="H11" s="5" t="s">
+      <c r="I11" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="I11" s="5" t="s">
+      <c r="J11" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="J11" s="5" t="s">
+      <c r="K11" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="M11" s="4"/>
-      <c r="T11" s="11" t="s">
+      <c r="N11" s="4"/>
+      <c r="U11" s="11" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:20">
+    <row r="12" spans="1:21">
       <c r="A12" s="5">
         <v>5</v>
       </c>
       <c r="B12" s="6"/>
-      <c r="C12" s="5">
+      <c r="C12" s="6"/>
+      <c r="D12" s="5">
         <v>292</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="E12" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="F12" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="H12" s="5" t="s">
+      <c r="I12" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="I12" s="5" t="s">
+      <c r="J12" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="J12" s="5" t="s">
+      <c r="K12" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="M12" s="4"/>
-      <c r="T12" s="11" t="s">
+      <c r="N12" s="4"/>
+      <c r="U12" s="11" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:20">
+    <row r="13" spans="1:21">
       <c r="A13" s="5"/>
-      <c r="B13" s="6"/>
-      <c r="C13" s="5"/>
-      <c r="M13" s="4"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="5"/>
+      <c r="N13" s="4"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="T8" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="T9" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="T10" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="U8" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="U9" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="U10" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
